--- a/2022 data/excel_outputs/314_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/314_boothwise_data.xlsx
@@ -14,11 +14,83 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="513">
   <si>
     <t>AC 314 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -343,7 +415,7 @@
     <t>P.V. BARAULI ROOM NO. 1</t>
   </si>
   <si>
-    <t>P.V. BARAULI ROOM NO. ■</t>
+    <t>NAN</t>
   </si>
   <si>
     <t>P.V. FARENDIYA</t>
@@ -1487,8 +1559,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1504,7 +1584,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1512,12 +1592,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1816,85 +1914,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="D2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="E2" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="F2" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="G2" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="H2" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="I2" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="J2" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="K2" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="L2" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="M2" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="N2" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="O2" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="P2" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="Q2" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="R2" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="S2" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="T2" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="U2" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="V2" t="s">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="W2" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="X2" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="Y2" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1902,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>860</v>
@@ -1979,7 +2149,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>583</v>
@@ -2056,7 +2226,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>928</v>
@@ -2133,7 +2303,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>965</v>
@@ -2210,7 +2380,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>735</v>
@@ -2287,7 +2457,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>915</v>
@@ -2364,7 +2534,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>852</v>
@@ -2441,7 +2611,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>774</v>
@@ -2518,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>1041</v>
@@ -2595,7 +2765,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>738</v>
@@ -2672,7 +2842,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>678</v>
@@ -2749,7 +2919,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>969</v>
@@ -2826,7 +2996,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>939</v>
@@ -2903,7 +3073,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>949</v>
@@ -2980,7 +3150,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>1210</v>
@@ -3057,7 +3227,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>423</v>
@@ -3134,7 +3304,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>1073</v>
@@ -3211,7 +3381,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>850</v>
@@ -3288,7 +3458,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>524</v>
@@ -3365,7 +3535,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>839</v>
@@ -3442,7 +3612,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>1177</v>
@@ -3519,7 +3689,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>501</v>
@@ -3596,7 +3766,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>1171</v>
@@ -3673,7 +3843,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>693</v>
@@ -3750,7 +3920,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>1047</v>
@@ -3827,7 +3997,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>769</v>
@@ -3904,7 +4074,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>820</v>
@@ -3981,7 +4151,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>996</v>
@@ -4058,7 +4228,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>663</v>
@@ -4135,7 +4305,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>1226</v>
@@ -4212,7 +4382,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>1107</v>
@@ -4289,7 +4459,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>1143</v>
@@ -4366,7 +4536,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C35">
         <v>655</v>
@@ -4443,7 +4613,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>969</v>
@@ -4520,7 +4690,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>647</v>
@@ -4597,7 +4767,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>765</v>
@@ -4674,7 +4844,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>716</v>
@@ -4751,7 +4921,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>624</v>
@@ -4828,7 +4998,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>829</v>
@@ -4905,7 +5075,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>734</v>
@@ -4982,7 +5152,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>688</v>
@@ -5059,7 +5229,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>1144</v>
@@ -5136,7 +5306,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>1148</v>
@@ -5213,7 +5383,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>843</v>
@@ -5290,7 +5460,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>543</v>
@@ -5367,7 +5537,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>739</v>
@@ -5444,7 +5614,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>933</v>
@@ -5521,7 +5691,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>1063</v>
@@ -5598,7 +5768,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>786</v>
@@ -5675,7 +5845,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>773</v>
@@ -5752,7 +5922,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>1192</v>
@@ -5829,7 +5999,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>1121</v>
@@ -5906,7 +6076,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>775</v>
@@ -5983,7 +6153,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>1063</v>
@@ -6060,7 +6230,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>408</v>
@@ -6137,7 +6307,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>566</v>
@@ -6214,7 +6384,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>1085</v>
@@ -6291,7 +6461,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>794</v>
@@ -6368,7 +6538,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>632</v>
@@ -6445,7 +6615,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>999</v>
@@ -6522,7 +6692,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>993</v>
@@ -6599,7 +6769,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>1052</v>
@@ -6676,7 +6846,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>1090</v>
@@ -6753,7 +6923,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>780</v>
@@ -6830,7 +7000,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>1153</v>
@@ -6907,7 +7077,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>995</v>
@@ -6984,7 +7154,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>1040</v>
@@ -7061,7 +7231,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>820</v>
@@ -7138,7 +7308,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>827</v>
@@ -7215,7 +7385,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>1164</v>
@@ -7292,7 +7462,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>1085</v>
@@ -7369,7 +7539,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>1168</v>
@@ -7446,7 +7616,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>1196</v>
@@ -7523,7 +7693,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C76">
         <v>1102</v>
@@ -7600,7 +7770,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>1128</v>
@@ -7677,7 +7847,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>1034</v>
@@ -7754,7 +7924,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>1090</v>
@@ -7831,7 +8001,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>751</v>
@@ -7908,7 +8078,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>552</v>
@@ -7985,7 +8155,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>657</v>
@@ -8062,7 +8232,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C83">
         <v>689</v>
@@ -8139,7 +8309,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>960</v>
@@ -8216,7 +8386,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>738</v>
@@ -8293,7 +8463,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>724</v>
@@ -8370,7 +8540,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>961</v>
@@ -8447,7 +8617,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>817</v>
@@ -8524,7 +8694,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>644</v>
@@ -8601,7 +8771,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>1148</v>
@@ -8678,7 +8848,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>542</v>
@@ -8755,7 +8925,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>576</v>
@@ -8832,7 +9002,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>1100</v>
@@ -8909,7 +9079,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C94">
         <v>882</v>
@@ -8986,7 +9156,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C95">
         <v>570</v>
@@ -9063,7 +9233,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C96">
         <v>551</v>
@@ -9140,7 +9310,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="C97">
         <v>515</v>
@@ -9217,7 +9387,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C98">
         <v>691</v>
@@ -9294,7 +9464,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>799</v>
@@ -9371,7 +9541,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C100">
         <v>840</v>
@@ -9448,7 +9618,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>753</v>
@@ -9525,7 +9695,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>880</v>
@@ -9602,7 +9772,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>1030</v>
@@ -9679,7 +9849,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>891</v>
@@ -9756,7 +9926,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>966</v>
@@ -9833,7 +10003,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>664</v>
@@ -9910,7 +10080,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>645</v>
@@ -9987,7 +10157,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>705</v>
@@ -10064,7 +10234,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>678</v>
@@ -10141,7 +10311,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>687</v>
@@ -10218,7 +10388,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>745</v>
@@ -10295,7 +10465,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>900</v>
@@ -10372,7 +10542,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C113">
         <v>321</v>
@@ -10449,7 +10619,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C114">
         <v>1060</v>
@@ -10526,7 +10696,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C115">
         <v>1151</v>
@@ -10603,7 +10773,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C116">
         <v>723</v>
@@ -10680,7 +10850,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>771</v>
@@ -10757,7 +10927,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="C118">
         <v>601</v>
@@ -10834,7 +11004,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C119">
         <v>474</v>
@@ -10911,7 +11081,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C120">
         <v>584</v>
@@ -10988,7 +11158,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C121">
         <v>653</v>
@@ -11065,7 +11235,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>641</v>
@@ -11142,7 +11312,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="C123">
         <v>665</v>
@@ -11219,7 +11389,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="C124">
         <v>617</v>
@@ -11296,7 +11466,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>543</v>
@@ -11373,7 +11543,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="C126">
         <v>729</v>
@@ -11450,7 +11620,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="C127">
         <v>670</v>
@@ -11527,7 +11697,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>861</v>
@@ -11604,7 +11774,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="C129">
         <v>851</v>
@@ -11681,7 +11851,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C130">
         <v>1028</v>
@@ -11758,7 +11928,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C131">
         <v>588</v>
@@ -11835,7 +12005,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="C132">
         <v>837</v>
@@ -11912,7 +12082,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>1120</v>
@@ -11989,7 +12159,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="C134">
         <v>1138</v>
@@ -12066,7 +12236,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C135">
         <v>513</v>
@@ -12143,7 +12313,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="C136">
         <v>959</v>
@@ -12220,7 +12390,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C137">
         <v>382</v>
@@ -12297,7 +12467,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="C138">
         <v>489</v>
@@ -12374,7 +12544,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="C139">
         <v>561</v>
@@ -12451,7 +12621,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="C140">
         <v>725</v>
@@ -12528,7 +12698,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>1093</v>
@@ -12605,7 +12775,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C142">
         <v>561</v>
@@ -12682,7 +12852,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C143">
         <v>1016</v>
@@ -12759,7 +12929,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C144">
         <v>1080</v>
@@ -12836,7 +13006,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="C145">
         <v>934</v>
@@ -12913,7 +13083,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C146">
         <v>865</v>
@@ -12990,7 +13160,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C147">
         <v>741</v>
@@ -13067,7 +13237,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C148">
         <v>726</v>
@@ -13144,7 +13314,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>653</v>
@@ -13221,7 +13391,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>875</v>
@@ -13298,7 +13468,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C151">
         <v>452</v>
@@ -13375,7 +13545,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>498</v>
@@ -13452,7 +13622,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="C153">
         <v>886</v>
@@ -13529,7 +13699,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C154">
         <v>791</v>
@@ -13606,7 +13776,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C155">
         <v>1187</v>
@@ -13683,7 +13853,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C156">
         <v>1200</v>
@@ -13760,7 +13930,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C157">
         <v>856</v>
@@ -13837,7 +14007,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C158">
         <v>823</v>
@@ -13914,7 +14084,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>864</v>
@@ -13991,7 +14161,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C160">
         <v>656</v>
@@ -14068,7 +14238,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C161">
         <v>698</v>
@@ -14145,7 +14315,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C162">
         <v>801</v>
@@ -14222,7 +14392,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="C163">
         <v>492</v>
@@ -14299,7 +14469,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="C164">
         <v>880</v>
@@ -14376,7 +14546,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C165">
         <v>821</v>
@@ -14453,7 +14623,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C166">
         <v>772</v>
@@ -14530,7 +14700,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C167">
         <v>677</v>
@@ -14607,7 +14777,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C168">
         <v>834</v>
@@ -14684,7 +14854,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C169">
         <v>1027</v>
@@ -14761,7 +14931,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C170">
         <v>912</v>
@@ -14838,7 +15008,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C171">
         <v>1104</v>
@@ -14915,7 +15085,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C172">
         <v>965</v>
@@ -14992,7 +15162,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C173">
         <v>629</v>
@@ -15069,7 +15239,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C174">
         <v>882</v>
@@ -15146,7 +15316,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="C175">
         <v>899</v>
@@ -15223,7 +15393,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="C176">
         <v>921</v>
@@ -15300,7 +15470,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C177">
         <v>1189</v>
@@ -15377,7 +15547,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C178">
         <v>841</v>
@@ -15454,7 +15624,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="C179">
         <v>837</v>
@@ -15531,7 +15701,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C180">
         <v>720</v>
@@ -15608,7 +15778,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C181">
         <v>443</v>
@@ -15685,7 +15855,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C182">
         <v>1181</v>
@@ -15762,7 +15932,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="C183">
         <v>701</v>
@@ -15839,7 +16009,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="C184">
         <v>816</v>
@@ -15916,7 +16086,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C185">
         <v>1149</v>
@@ -15993,7 +16163,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="C186">
         <v>1135</v>
@@ -16070,7 +16240,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="C187">
         <v>779</v>
@@ -16147,7 +16317,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C188">
         <v>525</v>
@@ -16224,7 +16394,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C189">
         <v>328</v>
@@ -16301,7 +16471,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="C190">
         <v>1082</v>
@@ -16378,7 +16548,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="C191">
         <v>864</v>
@@ -16455,7 +16625,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C192">
         <v>659</v>
@@ -16532,7 +16702,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="C193">
         <v>938</v>
@@ -16609,7 +16779,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="C194">
         <v>1159</v>
@@ -16686,7 +16856,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="C195">
         <v>585</v>
@@ -16763,7 +16933,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="C196">
         <v>1108</v>
@@ -16840,7 +17010,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C197">
         <v>949</v>
@@ -16917,7 +17087,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="C198">
         <v>1165</v>
@@ -16994,7 +17164,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C199">
         <v>652</v>
@@ -17071,7 +17241,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C200">
         <v>837</v>
@@ -17148,7 +17318,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C201">
         <v>410</v>
@@ -17225,7 +17395,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="C202">
         <v>1136</v>
@@ -17302,7 +17472,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C203">
         <v>666</v>
@@ -17379,7 +17549,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="C204">
         <v>1221</v>
@@ -17456,7 +17626,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="C205">
         <v>827</v>
@@ -17533,7 +17703,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="C206">
         <v>887</v>
@@ -17610,7 +17780,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="C207">
         <v>666</v>
@@ -17687,7 +17857,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="C208">
         <v>998</v>
@@ -17764,7 +17934,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="C209">
         <v>692</v>
@@ -17841,7 +18011,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C210">
         <v>828</v>
@@ -17918,7 +18088,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="C211">
         <v>1126</v>
@@ -17995,7 +18165,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="C212">
         <v>995</v>
@@ -18072,7 +18242,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="C213">
         <v>658</v>
@@ -18149,7 +18319,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C214">
         <v>646</v>
@@ -18226,7 +18396,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="C215">
         <v>883</v>
@@ -18303,7 +18473,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="C216">
         <v>381</v>
@@ -18380,7 +18550,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C217">
         <v>864</v>
@@ -18457,7 +18627,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="C218">
         <v>807</v>
@@ -18534,7 +18704,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="C219">
         <v>740</v>
@@ -18611,7 +18781,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="C220">
         <v>447</v>
@@ -18688,7 +18858,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="C221">
         <v>806</v>
@@ -18765,7 +18935,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="C222">
         <v>1053</v>
@@ -18842,7 +19012,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C223">
         <v>717</v>
@@ -18919,7 +19089,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="C224">
         <v>546</v>
@@ -18996,7 +19166,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C225">
         <v>727</v>
@@ -19073,7 +19243,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C226">
         <v>519</v>
@@ -19150,7 +19320,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C227">
         <v>765</v>
@@ -19227,7 +19397,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="C228">
         <v>652</v>
@@ -19304,7 +19474,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C229">
         <v>660</v>
@@ -19381,7 +19551,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C230">
         <v>652</v>
@@ -19458,7 +19628,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="C231">
         <v>1089</v>
@@ -19535,7 +19705,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>667</v>
@@ -19612,7 +19782,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C233">
         <v>1004</v>
@@ -19689,7 +19859,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>1108</v>
@@ -19766,7 +19936,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="C235">
         <v>870</v>
@@ -19843,7 +20013,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="C236">
         <v>651</v>
@@ -19920,7 +20090,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="C237">
         <v>691</v>
@@ -19997,7 +20167,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="C238">
         <v>698</v>
@@ -20074,7 +20244,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="C239">
         <v>688</v>
@@ -20151,7 +20321,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C240">
         <v>565</v>
@@ -20228,7 +20398,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C241">
         <v>1075</v>
@@ -20305,7 +20475,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C242">
         <v>816</v>
@@ -20382,7 +20552,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="C243">
         <v>782</v>
@@ -20459,7 +20629,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="C244">
         <v>741</v>
@@ -20536,7 +20706,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="C245">
         <v>621</v>
@@ -20613,7 +20783,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="C246">
         <v>737</v>
@@ -20690,7 +20860,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="C247">
         <v>748</v>
@@ -20767,7 +20937,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="C248">
         <v>590</v>
@@ -20844,7 +21014,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="C249">
         <v>609</v>
@@ -20921,7 +21091,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="C250">
         <v>1119</v>
@@ -20998,7 +21168,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="C251">
         <v>789</v>
@@ -21075,7 +21245,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="C252">
         <v>697</v>
@@ -21152,7 +21322,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="C253">
         <v>411</v>
@@ -21229,7 +21399,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="C254">
         <v>985</v>
@@ -21306,7 +21476,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="C255">
         <v>608</v>
@@ -21383,7 +21553,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="C256">
         <v>641</v>
@@ -21460,7 +21630,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="C257">
         <v>658</v>
@@ -21537,7 +21707,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="C258">
         <v>623</v>
@@ -21614,7 +21784,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C259">
         <v>649</v>
@@ -21691,7 +21861,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C260">
         <v>692</v>
@@ -21768,7 +21938,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C261">
         <v>911</v>
@@ -21845,7 +22015,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C262">
         <v>558</v>
@@ -21922,7 +22092,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C263">
         <v>1063</v>
@@ -21999,7 +22169,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="C264">
         <v>922</v>
@@ -22076,7 +22246,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="C265">
         <v>786</v>
@@ -22153,7 +22323,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C266">
         <v>817</v>
@@ -22230,7 +22400,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="C267">
         <v>791</v>
@@ -22307,7 +22477,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="C268">
         <v>762</v>
@@ -22384,7 +22554,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="C269">
         <v>642</v>
@@ -22461,7 +22631,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="C270">
         <v>1012</v>
@@ -22538,7 +22708,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C271">
         <v>1181</v>
@@ -22615,7 +22785,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C272">
         <v>1043</v>
@@ -22692,7 +22862,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C273">
         <v>963</v>
@@ -22769,7 +22939,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="C274">
         <v>1157</v>
@@ -22846,7 +23016,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C275">
         <v>646</v>
@@ -22923,7 +23093,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="C276">
         <v>615</v>
@@ -23000,7 +23170,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="C277">
         <v>1111</v>
@@ -23077,7 +23247,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="C278">
         <v>944</v>
@@ -23154,7 +23324,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="C279">
         <v>1244</v>
@@ -23231,7 +23401,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="C280">
         <v>551</v>
@@ -23308,7 +23478,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C281">
         <v>750</v>
@@ -23385,7 +23555,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="C282">
         <v>862</v>
@@ -23462,7 +23632,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="C283">
         <v>895</v>
@@ -23539,7 +23709,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C284">
         <v>684</v>
@@ -23616,7 +23786,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="C285">
         <v>621</v>
@@ -23693,7 +23863,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="C286">
         <v>784</v>
@@ -23770,7 +23940,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="C287">
         <v>876</v>
@@ -23847,7 +24017,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="C288">
         <v>928</v>
@@ -23924,7 +24094,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="C289">
         <v>769</v>
@@ -24001,7 +24171,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C290">
         <v>784</v>
@@ -24078,7 +24248,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="C291">
         <v>695</v>
@@ -24155,7 +24325,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C292">
         <v>751</v>
@@ -24232,7 +24402,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="C293">
         <v>578</v>
@@ -24309,7 +24479,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C294">
         <v>940</v>
@@ -24386,7 +24556,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="C295">
         <v>780</v>
@@ -24463,7 +24633,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="C296">
         <v>589</v>
@@ -24540,7 +24710,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="C297">
         <v>434</v>
@@ -24617,7 +24787,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="C298">
         <v>780</v>
@@ -24694,7 +24864,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="C299">
         <v>793</v>
@@ -24771,7 +24941,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="C300">
         <v>835</v>
@@ -24848,7 +25018,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="C301">
         <v>989</v>
@@ -24925,7 +25095,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="C302">
         <v>656</v>
@@ -25002,7 +25172,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="C303">
         <v>515</v>
@@ -25079,7 +25249,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="C304">
         <v>964</v>
@@ -25156,7 +25326,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="C305">
         <v>880</v>
@@ -25233,7 +25403,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="C306">
         <v>1145</v>
@@ -25310,7 +25480,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C307">
         <v>1003</v>
@@ -25387,7 +25557,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C308">
         <v>794</v>
@@ -25464,7 +25634,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="C309">
         <v>782</v>
@@ -25541,7 +25711,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="C310">
         <v>601</v>
@@ -25618,7 +25788,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="C311">
         <v>741</v>
@@ -25695,7 +25865,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="C312">
         <v>982</v>
@@ -25772,7 +25942,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="C313">
         <v>594</v>
@@ -25849,7 +26019,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C314">
         <v>1062</v>
@@ -25926,7 +26096,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="C315">
         <v>1012</v>
@@ -26003,7 +26173,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="C316">
         <v>1049</v>
@@ -26080,7 +26250,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C317">
         <v>789</v>
@@ -26157,7 +26327,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C318">
         <v>698</v>
@@ -26234,7 +26404,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="C319">
         <v>958</v>
@@ -26311,7 +26481,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="C320">
         <v>441</v>
@@ -26388,7 +26558,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="C321">
         <v>1085</v>
@@ -26465,7 +26635,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="C322">
         <v>899</v>
@@ -26542,7 +26712,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="C323">
         <v>636</v>
@@ -26619,7 +26789,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="C324">
         <v>617</v>
@@ -26696,7 +26866,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="C325">
         <v>923</v>
@@ -26773,7 +26943,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="C326">
         <v>556</v>
@@ -26850,7 +27020,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="C327">
         <v>745</v>
@@ -26927,7 +27097,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="C328">
         <v>666</v>
@@ -27004,7 +27174,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="C329">
         <v>600</v>
@@ -27081,7 +27251,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="C330">
         <v>954</v>
@@ -27158,7 +27328,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="C331">
         <v>1006</v>
@@ -27235,7 +27405,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="C332">
         <v>929</v>
@@ -27312,7 +27482,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="C333">
         <v>803</v>
@@ -27389,7 +27559,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="C334">
         <v>995</v>
@@ -27466,7 +27636,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="C335">
         <v>784</v>
@@ -27543,7 +27713,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="C336">
         <v>1215</v>
@@ -27620,7 +27790,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="C337">
         <v>1221</v>
@@ -27697,7 +27867,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="C338">
         <v>863</v>
@@ -27774,7 +27944,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="C339">
         <v>990</v>
@@ -27851,7 +28021,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="C340">
         <v>431</v>
@@ -27928,7 +28098,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="C341">
         <v>943</v>
@@ -28005,7 +28175,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C342">
         <v>846</v>
@@ -28082,7 +28252,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="C343">
         <v>739</v>
@@ -28159,7 +28329,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C344">
         <v>780</v>
@@ -28236,7 +28406,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="C345">
         <v>819</v>
@@ -28313,7 +28483,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="C346">
         <v>937</v>
@@ -28390,7 +28560,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="C347">
         <v>844</v>
@@ -28467,7 +28637,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="C348">
         <v>822</v>
@@ -28544,7 +28714,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="C349">
         <v>651</v>
@@ -28621,7 +28791,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="C350">
         <v>1199</v>
@@ -28698,7 +28868,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C351">
         <v>1042</v>
@@ -28775,7 +28945,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="C352">
         <v>668</v>
@@ -28852,7 +29022,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="C353">
         <v>617</v>
@@ -28929,7 +29099,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="C354">
         <v>831</v>
@@ -29006,7 +29176,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="C355">
         <v>525</v>
@@ -29083,7 +29253,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="C356">
         <v>746</v>
@@ -29160,7 +29330,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="C357">
         <v>1041</v>
@@ -29237,7 +29407,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="C358">
         <v>917</v>
@@ -29314,7 +29484,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="C359">
         <v>737</v>
@@ -29391,7 +29561,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="C360">
         <v>862</v>
@@ -29468,7 +29638,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="C361">
         <v>697</v>
@@ -29545,7 +29715,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C362">
         <v>931</v>
@@ -29622,7 +29792,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="C363">
         <v>818</v>
@@ -29699,7 +29869,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C364">
         <v>680</v>
@@ -29776,7 +29946,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="C365">
         <v>672</v>
@@ -29853,7 +30023,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="C366">
         <v>948</v>
@@ -29930,7 +30100,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="C367">
         <v>1080</v>
@@ -30007,7 +30177,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="C368">
         <v>1057</v>
@@ -30084,7 +30254,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C369">
         <v>849</v>
@@ -30161,7 +30331,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C370">
         <v>666</v>
@@ -30238,7 +30408,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="C371">
         <v>815</v>
@@ -30315,7 +30485,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C372">
         <v>655</v>
@@ -30392,7 +30562,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="C373">
         <v>783</v>
@@ -30469,7 +30639,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="C374">
         <v>657</v>
@@ -30546,7 +30716,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="C375">
         <v>745</v>
@@ -30623,7 +30793,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C376">
         <v>623</v>
@@ -30700,7 +30870,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="C377">
         <v>800</v>
@@ -30777,7 +30947,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="C378">
         <v>1219</v>
@@ -30854,7 +31024,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="C379">
         <v>1223</v>
@@ -30931,7 +31101,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="C380">
         <v>995</v>
@@ -31008,7 +31178,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C381">
         <v>818</v>
@@ -31085,7 +31255,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="C382">
         <v>827</v>
@@ -31162,7 +31332,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="C383">
         <v>815</v>
@@ -31239,7 +31409,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="C384">
         <v>982</v>
@@ -31316,7 +31486,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="C385">
         <v>964</v>
@@ -31393,7 +31563,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="C386">
         <v>687</v>
@@ -31470,7 +31640,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="C387">
         <v>1134</v>
@@ -31547,7 +31717,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="C388">
         <v>1077</v>
@@ -31624,7 +31794,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="C389">
         <v>818</v>
@@ -31701,7 +31871,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C390">
         <v>852</v>
@@ -31778,7 +31948,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="C391">
         <v>787</v>
@@ -31855,7 +32025,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="C392">
         <v>750</v>
@@ -31932,7 +32102,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C393">
         <v>860</v>
@@ -32009,7 +32179,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="C394">
         <v>1135</v>
@@ -32086,7 +32256,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="C395">
         <v>895</v>
@@ -32163,7 +32333,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C396">
         <v>820</v>
@@ -32240,7 +32410,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="C397">
         <v>752</v>
@@ -32317,7 +32487,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="C398">
         <v>758</v>
@@ -32394,7 +32564,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="C399">
         <v>838</v>
@@ -32471,7 +32641,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="C400">
         <v>553</v>
@@ -32548,7 +32718,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="C401">
         <v>790</v>
@@ -32625,7 +32795,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="C402">
         <v>917</v>
@@ -32702,7 +32872,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="C403">
         <v>831</v>
@@ -32779,7 +32949,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="C404">
         <v>617</v>
@@ -32856,7 +33026,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="C405">
         <v>630</v>
@@ -32933,7 +33103,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="C406">
         <v>1179</v>
@@ -33010,7 +33180,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="C407">
         <v>773</v>
@@ -33087,7 +33257,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="C408">
         <v>718</v>
@@ -33164,7 +33334,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="C409">
         <v>439</v>
@@ -33241,7 +33411,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C410">
         <v>881</v>
@@ -33318,7 +33488,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C411">
         <v>881</v>
@@ -33395,7 +33565,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="C412">
         <v>844</v>
@@ -33472,7 +33642,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C413">
         <v>777</v>
@@ -33549,7 +33719,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="C414">
         <v>1015</v>
@@ -33626,7 +33796,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="C415">
         <v>820</v>
@@ -33703,7 +33873,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="C416">
         <v>825</v>
@@ -33780,7 +33950,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="C417">
         <v>834</v>
@@ -33857,7 +34027,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="C418">
         <v>983</v>
@@ -33934,7 +34104,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="C419">
         <v>842</v>
@@ -34011,7 +34181,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="C420">
         <v>614</v>
@@ -34088,7 +34258,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="C421">
         <v>1122</v>
@@ -34165,7 +34335,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C422">
         <v>1212</v>
@@ -34242,7 +34412,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="C423">
         <v>721</v>
@@ -34319,7 +34489,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="C424">
         <v>696</v>
@@ -34396,7 +34566,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="C425">
         <v>842</v>
@@ -34473,7 +34643,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="C426">
         <v>837</v>
@@ -34550,7 +34720,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="C427">
         <v>842</v>
@@ -34627,7 +34797,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="C428">
         <v>694</v>
@@ -34704,7 +34874,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="C429">
         <v>998</v>
@@ -34781,7 +34951,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="C430">
         <v>724</v>
@@ -34858,7 +35028,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="C431">
         <v>1104</v>
@@ -34935,7 +35105,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="C432">
         <v>1000</v>
@@ -35012,7 +35182,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="C433">
         <v>925</v>
@@ -35089,7 +35259,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="C434">
         <v>812</v>
@@ -35166,7 +35336,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="C435">
         <v>794</v>
@@ -35243,7 +35413,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="C436">
         <v>839</v>
@@ -35320,7 +35490,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="C437">
         <v>1191</v>
@@ -35397,7 +35567,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="C438">
         <v>1098</v>
@@ -35474,7 +35644,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="C439">
         <v>897</v>
@@ -35551,7 +35721,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="C440">
         <v>751</v>
@@ -35628,7 +35798,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="C441">
         <v>1057</v>
@@ -35705,7 +35875,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="C442">
         <v>456</v>
@@ -35782,7 +35952,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="C443">
         <v>548</v>
@@ -35859,7 +36029,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="C444">
         <v>796</v>
@@ -35936,7 +36106,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="C445">
         <v>556</v>
@@ -36013,7 +36183,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="C446">
         <v>1080</v>
@@ -36090,7 +36260,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="C447">
         <v>997</v>
@@ -36167,7 +36337,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="C448">
         <v>1077</v>
@@ -36244,7 +36414,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="C449">
         <v>1131</v>
@@ -36321,7 +36491,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="C450">
         <v>490</v>
@@ -36398,7 +36568,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="C451">
         <v>875</v>
@@ -36475,7 +36645,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="C452">
         <v>876</v>
@@ -36552,7 +36722,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="C453">
         <v>1008</v>
@@ -36629,7 +36799,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="C454">
         <v>1014</v>
@@ -36706,7 +36876,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="C455">
         <v>423</v>
@@ -36783,7 +36953,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="C456">
         <v>871</v>
@@ -36860,7 +37030,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="C457">
         <v>1182</v>
@@ -36937,7 +37107,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="C458">
         <v>1217</v>
@@ -37014,7 +37184,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="C459">
         <v>957</v>
@@ -37091,7 +37261,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="C460">
         <v>1014</v>
@@ -37168,7 +37338,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="C461">
         <v>1015</v>
@@ -37245,7 +37415,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="C462">
         <v>683</v>
@@ -37322,7 +37492,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="C463">
         <v>490</v>
@@ -37399,7 +37569,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="C464">
         <v>1132</v>
@@ -37476,7 +37646,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="C465">
         <v>696</v>
@@ -37553,7 +37723,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="C466">
         <v>848</v>
@@ -37630,7 +37800,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="C467">
         <v>656</v>
@@ -37707,7 +37877,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="C468">
         <v>1081</v>
